--- a/Assets/test260903/chapter0106.xlsx
+++ b/Assets/test260903/chapter0106.xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="412" documentId="11_AA3EC6FCFDC488042E83A027A8BF20349734F0B7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07B4D029-B20A-4E75-A3FB-6A1D8EFF5C95}"/>
+  <bookViews>
+    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="chapter0106" sheetId="1" r:id="rId4"/>
+    <sheet name="chapter0106" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="1wnk63aERf7/uTyT6okFjiq/Ayajw31Os+0y4XC6imY="/>
@@ -16,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="168">
   <si>
     <t>Command</t>
   </si>
@@ -66,9 +75,6 @@
     <t>WaitInput</t>
   </si>
   <si>
-    <t>BgOff</t>
-  </si>
-  <si>
     <t>Chapter1-6です</t>
   </si>
   <si>
@@ -76,27 +82,735 @@
   </si>
   <si>
     <t>*chapter0201_Start</t>
+  </si>
+  <si>
+    <t>Bgm</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>BGM1</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Bg</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>背景：夕焼けの教室</t>
+  </si>
+  <si>
+    <t>夕方の教室。みんな帰ってしまって、
+僕は一人きりで窓の外を眺めていた</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>グラウンドを走る運動部、
+遠くで聞こえる吹奏楽部の演奏</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>いつも通りの放課後を過ごしながら、
+前に考えたことを、また考えていた</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>夢は、基本的に叶わない</t>
+  </si>
+  <si>
+    <t>一生懸命、努力することはもちろん、
+運がないと無理なんだ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>……とりあえず、
+今の僕には両方とも無いっぽい</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>高校三年生の夏、僕の本が世に出た。
+評判はよかったけど、売れ行きは悪かった</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>編集者も「なぜ売れないのか……」と、
+首をひねっている</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>とりあえず続刊は出せそうにないので、
+別の企画を考えることになった</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>そして……</t>
+  </si>
+  <si>
+    <t>センセ～！　お疲れ様！
+まだまだ一日、頑張っていこうねっ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>浪川有希</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>通常</t>
+    <rPh sb="0" eb="2">
+      <t>ツウジョウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Selection</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0106-1-a</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0106-1-b</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>お疲れ様っ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>だから、何を頑張るんだ？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>うんうん、元気な挨拶が聞けてよかった</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>やっぱ挨拶は基本やね～
+何がどうなっても、大事っちゃ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Jump</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0106-1合流</t>
+    <rPh sb="10" eb="12">
+      <t>ゴウリュウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>決まってるやん。
+放課後の特別夏期講習！</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>この夏が終わったら、本格的に受験やん。
+今のうちに、たくさん頑張っとかんと</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>有希は、またうちの高校に戻ってきた</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>芸能活動は休止中だ。
+現在は受験勉強に集中している</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>目指すのは、東京の大学への進学。
+それは僕も一緒だ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>東京の夜のことは、
+あれから一度も話していないけれど……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>あの日から、僕と有希は、
+子どもの頃に戻ったように過ごしている</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>お互いを励まし合って、相談して、
+それぞれの目標に向かって努力している</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>絶対に二人揃って受かろうね！
+で、また東京に行く！</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>センセーの仕事は、
+東京の方が絶対にやりやすいし……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>私も学生演劇とか、ワークショップとか
+東京でいくつかツテが出来たし</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>そこで勉強するためにも、
+大学進学で上京しなくちゃ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0106-2-a</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>だからって、もう無理は……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>あっははは、大丈夫よ。
+もう無理はせんって。骨身に染みたもん</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>次は誰かのペースやなくて、
+私のペースでやってみるって決めたんよ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>そんで失敗したら、
+今度こそスパッと諦めるつもり</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>いっぺん諦めて、よく分かったんちゃ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>変に無理してもイイことない。
+それに、何事もなるようになるってさ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>……有希の言う通りだ。
+僕らは、何とかなってしまった</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>有希がキャンセルした仕事は、
+すぐに別の人が埋めてしまった</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>というか有希が休業したことも、
+世間ではあまり認知されていない</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>有希は、もうすっかり過去の人なのだ。
+ついでにいうと……僕もだ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>僕の小説も売れなかったけど、
+だからって出版社が傾くこともなかった</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>僕は過去の人にすらなれなかった。
+世間的には、無名の新人にすぎない</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>僕らは確かに上手くいかなかった。
+でも、何事もなかったように世界は動く</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ホッとしたけれど、ちょっとだけ悔しい。
+僕も有希も、そう思っている……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>あ、そうそう！　センセー、
+昨日も深夜までSNSで何か呟いてたよね？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>早寝早起きしないと、体に悪いよ。
+作家は体を崩しやすいって聞くし……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0106-3-a</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>了解</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ね、お互い気をつけよう</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>有希は役者を、僕は作家を。
+相変わらず、お互いに夢を追っている</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>でも、それは以前とは全く異なる。
+ゆったりと、のんびりとした歩みだ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>あの夜、マネージャーに言われた通り、
+今の僕らのやり方は甘いのかもしれない</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>このまま成功するかって聞かれたら、
+正直、絶対にとは言えない</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>でも、出来る気もするんだ。
+こうして有希と一緒なら</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>だって……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>センセー、今日も講習ば終わったら、
+家に遊びに行っていい？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>センセーの小説が読みたいし、
+あと、私の演技のことでも相談したいし</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>……いいっちゃね？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>有希といると、それだけで幸せで、
+心の深い部分から元気が湧いてくる</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>……僕らはまだ走れる。自分たちの足で</t>
+  </si>
+  <si>
+    <t>これから先、どんなふうになっても、
+たとえ夢が叶わなくても……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ね～～何でまた、たそがれとると？
+家、行って大丈夫？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0106-4-a</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>あ、はい</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>うん♪　よかった</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>それじゃついでに……センセー、
+ちょっと恥ずかしいこと言っていい？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0106-5-a</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>何？</t>
+  </si>
+  <si>
+    <t>いや、私って……センセーがおって、
+本当に良かったと思ってね</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0106-6-a</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>急にかしこまって、どうしたの？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>だってさ、今って二人きりやん。
+そういう話をしてイイ空気かなぁって</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>あの時、東京のホテルでは、
+疲れててマトモに話せんやったし……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>その後も何だかんだでバタバタして……
+何て言うか……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>私が普通に戻るので精一杯で……
+ちゃんと話ができんかったなぁって</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>BGM6</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>だから、二人きりの今、
+話しておこうかなって思ってさ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>東京でやれんかった、
+大事な話があるんちゃ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>本当なら、
+あの時やらんといけんのやけど……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0106-7-a</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0106-7-b</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>あれより大事な話ってあるの？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>愛の告白じゃあるまいし……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>……えっ？
+私、東京で何か話したの！？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>東京やと、ホテルで会って、
+次の日の朝には分かれて、そのまま……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>何も話せんかったはずやけど……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0106-7合流</t>
+    <rPh sb="10" eb="12">
+      <t>ゴウリュウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ちょっと、何で先に言うと！？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>それを先に言われたら、
+順序がグチャグチャになるやん</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>えっと、確かにそうなんやけど……
+何て言うか……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>……落ち着こう。
+まずは状況を正確に把握しなければ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>有希……ひょっとして、
+あの時の会話の内容を覚えていないの？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>えっ、そんなこと……ある！？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ここはちゃんと確認しなければ。
+えっと……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0106-8-a</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>まさか……告白したの、覚えてないの？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>はっ……私、告白したん？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>えっ、ええええええ！？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ちょっ、ちょっと待って！
+私、どんな言い方したん！？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0106-9-a</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0106-9-b</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>秘密</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>……いつか話そう</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0106-9合流</t>
+    <rPh sb="10" eb="12">
+      <t>ゴウリュウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>なんねそれーっ！
+そんなん反則やん！　いけんって！</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0106-10-a</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>忘れられてるこっちもショックだ！</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>そ、そっか！　ごめん！</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>それじゃ、改めて……ごくっ</t>
+  </si>
+  <si>
+    <t>……って！　や、やっぱ無理っちゃ！
+この流れから告白は無理やってー！</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>この話は、また別の時にしよう！</t>
+  </si>
+  <si>
+    <t>今は夏季補修！
+ほら、行こうよ！　センセー！</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0106-11-a</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0106-11-b</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ちゃんと話そう</t>
+  </si>
+  <si>
+    <t>っていうか、僕だって好きだ</t>
+  </si>
+  <si>
+    <t>でも、こっから話すことなんて……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>いや……あるよね。
+話すことなら、あるね</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0106-11合流</t>
+    <rPh sb="11" eb="13">
+      <t>ゴウリュウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ちょっ！　センセー！
+そういうこと言うの反則っちゃ！</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>困る、いや、困るっていうのは、
+嫌って意味じゃなくて……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ごほんごほん、ともかく！
+私……ちゃんと話すね</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>私、センセーのことが好き。
+子どもの頃から、ずっと好きやった</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>センセーのためなら……いや、違うね。
+そんなカッコいいことやなくて……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>あなたに負けたくないし、
+あなたの前では、最高の私でいたい</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>それに……あなたと一緒やと、
+私、元気が出てくるんちゃね</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>あなたと一緒の時が一番楽しい</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>色々なことを、あなたと経験したい。
+辛いことも、楽しいことも、全部、全部</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>やけん……あなたと、
+これからもずっと一緒にいたい</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>好きっちゃ、あなたのことが</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>……今度は、忘れんようにせんとね</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>そう有希が呟いた、次の瞬間……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>不意に甘く爽やかな香りがした。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>その香りは、有希の匂いだった。
+彼女の体が触れ合うほど近くに……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>そう気づいた時には、触れていた。
+有希が、僕に抱き着いていた</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>一瞬で全身が固まる。
+どう反応していいのか分からない</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>でも、有希は動いた。そして……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>僕の唇に、
+有希の唇が重なる感触がした</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>……そんなわけはないのに、
+教室の時計の秒針の音が聞こえた</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>一枚絵</t>
+    <rPh sb="0" eb="2">
+      <t>イチマイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>エ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -104,49 +818,74 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="13">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -336,28 +1075,28 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L1063"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="11.5"/>
-    <col customWidth="1" min="2" max="2" width="14.0"/>
-    <col customWidth="1" min="3" max="7" width="5.13"/>
-    <col customWidth="1" min="8" max="8" width="8.63"/>
-    <col customWidth="1" min="9" max="9" width="37.75"/>
-    <col customWidth="1" min="10" max="10" width="8.25"/>
-    <col customWidth="1" min="11" max="11" width="6.0"/>
-    <col customWidth="1" min="12" max="12" width="11.38"/>
-    <col customWidth="1" min="13" max="26" width="8.0"/>
+    <col min="1" max="1" width="11.44140625" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" customWidth="1"/>
+    <col min="3" max="7" width="5.109375" customWidth="1"/>
+    <col min="8" max="8" width="8.6640625" customWidth="1"/>
+    <col min="9" max="9" width="40" customWidth="1"/>
+    <col min="10" max="10" width="8.21875" customWidth="1"/>
+    <col min="11" max="11" width="6" customWidth="1"/>
+    <col min="12" max="12" width="11.33203125" customWidth="1"/>
+    <col min="13" max="26" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1">
+    <row r="1" spans="1:12" ht="13.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -395,686 +1134,1447 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="13.5" customHeight="1">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B2" s="1"/>
       <c r="H2" s="1"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" ht="13.5" customHeight="1">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" ht="13.5" customHeight="1">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="6">
-        <v>3.0</v>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="4">
+        <v>3</v>
       </c>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" ht="13.5" customHeight="1">
-      <c r="A5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
+    <row r="5" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
       <c r="H5" s="4"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-    </row>
-    <row r="6" ht="13.5" customHeight="1">
-      <c r="B6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K6" s="1"/>
-    </row>
-    <row r="7" ht="13.5" customHeight="1">
-      <c r="A7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" s="1"/>
+    </row>
+    <row r="6" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A7" s="1"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
       <c r="I7" s="1"/>
-    </row>
-    <row r="8" ht="13.5" customHeight="1">
-      <c r="I8" s="1"/>
-    </row>
-    <row r="9" ht="13.5" customHeight="1">
-      <c r="I9" s="1"/>
-    </row>
-    <row r="10" ht="13.5" customHeight="1">
-      <c r="I10" s="1"/>
-    </row>
-    <row r="11" ht="13.5" customHeight="1">
-      <c r="I11" s="1"/>
-    </row>
-    <row r="12" ht="13.5" customHeight="1">
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-    </row>
-    <row r="13" ht="13.5" customHeight="1">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-    </row>
-    <row r="14" ht="13.5" customHeight="1">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="I14" s="1"/>
+      <c r="J7" s="1"/>
+    </row>
+    <row r="8" spans="1:12" ht="13.5" customHeight="1">
+      <c r="B8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" spans="1:12" ht="28.8" customHeight="1">
+      <c r="H9" s="1"/>
+      <c r="I9" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="30.6" customHeight="1">
+      <c r="I10" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="28.8" customHeight="1">
+      <c r="I11" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="13.5" customHeight="1">
+      <c r="I12" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="28.8" customHeight="1">
+      <c r="I13" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="28.8" customHeight="1">
+      <c r="I14" s="6" t="s">
+        <v>28</v>
+      </c>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" ht="13.5" customHeight="1">
+    <row r="15" spans="1:12" ht="30" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
-      <c r="I15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="I15" s="6" t="s">
+        <v>29</v>
+      </c>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" ht="13.5" customHeight="1">
+    <row r="16" spans="1:12" ht="30.6" customHeight="1">
+      <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
-      <c r="I16" s="1"/>
+      <c r="I16" s="6" t="s">
+        <v>30</v>
+      </c>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" ht="13.5" customHeight="1">
+    <row r="17" spans="1:10" ht="30" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
-      <c r="I17" s="1"/>
-    </row>
-    <row r="18" ht="13.5" customHeight="1">
-      <c r="A18" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="I17" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J17" s="1"/>
+    </row>
+    <row r="18" spans="1:10" ht="13.5" customHeight="1">
       <c r="B18" s="1"/>
-      <c r="I18" s="1"/>
-    </row>
-    <row r="19" ht="13.5" customHeight="1">
+      <c r="C18" s="1"/>
+      <c r="I18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J18" s="1"/>
+    </row>
+    <row r="19" spans="1:10" ht="28.8" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="I19" s="1"/>
-    </row>
-    <row r="20" ht="13.5" customHeight="1">
-      <c r="A20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-    </row>
-    <row r="21" ht="13.5" customHeight="1">
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="I21" s="1"/>
-    </row>
-    <row r="22" ht="13.5" customHeight="1">
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
+      <c r="B19" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A20" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A21" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A22" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H22" s="1"/>
       <c r="I22" s="1"/>
     </row>
-    <row r="23" ht="13.5" customHeight="1">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-    </row>
-    <row r="24" ht="13.5" customHeight="1">
-      <c r="A24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-    </row>
-    <row r="25" ht="13.5" customHeight="1">
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
+    <row r="23" spans="1:10" ht="16.2" customHeight="1">
+      <c r="B23" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="30" customHeight="1">
+      <c r="B24" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A25" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>44</v>
+      </c>
       <c r="I25" s="1"/>
-    </row>
-    <row r="26" ht="13.5" customHeight="1">
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
+      <c r="J25" s="1"/>
+    </row>
+    <row r="26" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A26" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="I26" s="1"/>
-    </row>
-    <row r="27" ht="13.5" customHeight="1">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-    </row>
-    <row r="28" ht="13.5" customHeight="1">
-      <c r="A28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-    </row>
-    <row r="29" ht="13.5" customHeight="1">
+      <c r="J26" s="1"/>
+    </row>
+    <row r="27" spans="1:10" ht="30" customHeight="1">
+      <c r="B27" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="30" customHeight="1">
+      <c r="B28" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A29" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>44</v>
+      </c>
       <c r="I29" s="1"/>
-    </row>
-    <row r="30" ht="13.5" customHeight="1">
+      <c r="J29" s="1"/>
+    </row>
+    <row r="30" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A30" s="11" t="s">
+        <v>44</v>
+      </c>
       <c r="I30" s="1"/>
-    </row>
-    <row r="31" ht="13.5" customHeight="1">
-      <c r="I31" s="1"/>
-    </row>
-    <row r="32" ht="13.5" customHeight="1">
-      <c r="I32" s="1"/>
-    </row>
-    <row r="33" ht="13.5" customHeight="1">
-      <c r="I33" s="1"/>
-    </row>
-    <row r="34" ht="13.5" customHeight="1">
-      <c r="I34" s="1"/>
-    </row>
-    <row r="35" ht="13.5" customHeight="1">
-      <c r="I35" s="1"/>
-    </row>
-    <row r="36" ht="13.5" customHeight="1">
-      <c r="I36" s="1"/>
-    </row>
-    <row r="37" ht="13.5" customHeight="1">
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="I37" s="1"/>
-    </row>
-    <row r="38" ht="13.5" customHeight="1">
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="I38" s="1"/>
-    </row>
-    <row r="39" ht="13.5" customHeight="1">
-      <c r="I39" s="1"/>
-    </row>
-    <row r="40" ht="13.5" customHeight="1">
-      <c r="I40" s="1"/>
-    </row>
-    <row r="41" ht="13.5" customHeight="1">
-      <c r="I41" s="1"/>
-    </row>
-    <row r="42" ht="13.5" customHeight="1">
+      <c r="J30" s="1"/>
+    </row>
+    <row r="31" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I31" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="28.8" customHeight="1">
+      <c r="I32" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="28.8" customHeight="1">
+      <c r="I33" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="28.8" customHeight="1">
+      <c r="I34" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="30.6" customHeight="1">
+      <c r="I35" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="30" customHeight="1">
+      <c r="I36" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="30" customHeight="1">
+      <c r="B37" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="30.6" customHeight="1">
+      <c r="B38" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B39" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B40" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A41" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A42" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="I42" s="1"/>
     </row>
-    <row r="43" ht="13.5" customHeight="1">
-      <c r="I43" s="1"/>
-    </row>
-    <row r="44" ht="13.5" customHeight="1">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-      <c r="I44" s="1"/>
-    </row>
-    <row r="45" ht="13.5" customHeight="1">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
-      <c r="I45" s="1"/>
-    </row>
-    <row r="46" ht="13.5" customHeight="1">
+    <row r="43" spans="1:10" ht="31.2" customHeight="1">
+      <c r="B43" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B44" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B45" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="13.5" customHeight="1">
       <c r="A46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-    </row>
-    <row r="47" ht="13.5" customHeight="1">
-      <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-      <c r="I47" s="1"/>
-    </row>
-    <row r="48" ht="13.5" customHeight="1">
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
-      <c r="I48" s="1"/>
+      <c r="B46" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="30" customHeight="1">
+      <c r="A47" s="1"/>
+      <c r="B47" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="30.6" customHeight="1">
+      <c r="A48" s="1"/>
+      <c r="I48" s="5" t="s">
+        <v>64</v>
+      </c>
       <c r="J48" s="1"/>
     </row>
-    <row r="49" ht="13.5" customHeight="1">
+    <row r="49" spans="1:10" ht="30" customHeight="1">
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
-    </row>
-    <row r="50" ht="13.5" customHeight="1">
-      <c r="A50" s="1"/>
+      <c r="I49" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="30" customHeight="1">
       <c r="B50" s="1"/>
-      <c r="I50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="I50" s="5" t="s">
+        <v>66</v>
+      </c>
       <c r="J50" s="1"/>
     </row>
-    <row r="51" ht="13.5" customHeight="1">
-      <c r="A51" s="1"/>
-      <c r="I51" s="1"/>
+    <row r="51" spans="1:10" ht="30" customHeight="1">
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="I51" s="5" t="s">
+        <v>67</v>
+      </c>
       <c r="J51" s="1"/>
     </row>
-    <row r="52" ht="13.5" customHeight="1">
+    <row r="52" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A52" s="1"/>
       <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
-      <c r="I52" s="1"/>
-    </row>
-    <row r="53" ht="13.5" customHeight="1">
-      <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
-      <c r="I53" s="1"/>
-    </row>
-    <row r="54" ht="13.5" customHeight="1">
-      <c r="A54" s="1"/>
+      <c r="I52" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="J52" s="1"/>
+    </row>
+    <row r="53" spans="1:10" ht="30" customHeight="1">
+      <c r="A53" s="1"/>
+      <c r="I53" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="J53" s="1"/>
+    </row>
+    <row r="54" spans="1:10" ht="30" customHeight="1">
       <c r="B54" s="1"/>
-      <c r="I54" s="1"/>
-    </row>
-    <row r="55" ht="13.5" customHeight="1">
-      <c r="A55" s="1"/>
-      <c r="I55" s="1"/>
-    </row>
-    <row r="56" ht="13.5" customHeight="1">
-      <c r="I56" s="1"/>
-    </row>
-    <row r="57" ht="13.5" customHeight="1">
-      <c r="I57" s="1"/>
-    </row>
-    <row r="58" ht="13.5" customHeight="1">
-      <c r="A58" s="1"/>
-      <c r="B58" s="1"/>
-      <c r="I58" s="1"/>
-    </row>
-    <row r="59" ht="13.5" customHeight="1">
-      <c r="A59" s="1"/>
-      <c r="B59" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="I54" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="31.2" customHeight="1">
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="I55" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="31.2" customHeight="1">
+      <c r="A56" s="1"/>
+      <c r="B56" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I56" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A57" s="1"/>
+      <c r="B57" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I57" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A58" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A59" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="I59" s="1"/>
     </row>
-    <row r="60" ht="13.5" customHeight="1">
-      <c r="B60" s="1"/>
-      <c r="C60" s="1"/>
-      <c r="I60" s="1"/>
-    </row>
-    <row r="61" ht="13.5" customHeight="1">
+    <row r="60" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A60" s="1"/>
+      <c r="B60" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I60" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A61" s="1"/>
       <c r="B61" s="1"/>
-      <c r="C61" s="1"/>
-      <c r="I61" s="1"/>
-    </row>
-    <row r="62" ht="13.5" customHeight="1">
+      <c r="I61" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="30" customHeight="1">
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
-      <c r="I62" s="1"/>
-    </row>
-    <row r="63" ht="13.5" customHeight="1">
+      <c r="I62" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="30" customHeight="1">
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
-      <c r="I63" s="1"/>
-    </row>
-    <row r="64" ht="13.5" customHeight="1">
-      <c r="A64" s="1"/>
+      <c r="I63" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="30" customHeight="1">
       <c r="B64" s="1"/>
-      <c r="I64" s="1"/>
-    </row>
-    <row r="65" ht="13.5" customHeight="1">
-      <c r="A65" s="1"/>
+      <c r="C64" s="1"/>
+      <c r="I64" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="30" customHeight="1">
       <c r="B65" s="1"/>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
-    </row>
-    <row r="66" ht="13.5" customHeight="1">
+      <c r="C65" s="1"/>
+      <c r="I65" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A66" s="1"/>
       <c r="B66" s="1"/>
-      <c r="C66" s="1"/>
-      <c r="I66" s="1"/>
-    </row>
-    <row r="67" ht="13.5" customHeight="1">
-      <c r="B67" s="1"/>
-      <c r="C67" s="1"/>
-      <c r="I67" s="1"/>
-    </row>
-    <row r="68" ht="13.5" customHeight="1">
-      <c r="A68" s="1"/>
-      <c r="B68" s="1"/>
-      <c r="I68" s="1"/>
-    </row>
-    <row r="69" ht="13.5" customHeight="1">
-      <c r="A69" s="1"/>
-      <c r="B69" s="1"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-    </row>
-    <row r="70" ht="13.5" customHeight="1">
+      <c r="I66" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="30" customHeight="1">
+      <c r="A67" s="1"/>
+      <c r="B67" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H67" s="1"/>
+      <c r="I67" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B68" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I68" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B69" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I69" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A70" s="1"/>
       <c r="B70" s="1"/>
-      <c r="C70" s="1"/>
-      <c r="I70" s="1"/>
-    </row>
-    <row r="71" ht="13.5" customHeight="1">
+      <c r="I70" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A71" s="1"/>
       <c r="B71" s="1"/>
-      <c r="C71" s="1"/>
-      <c r="I71" s="1"/>
-    </row>
-    <row r="72" ht="13.5" customHeight="1">
+      <c r="H71" s="1"/>
+      <c r="I71" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" ht="28.8" customHeight="1">
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
-      <c r="I72" s="1"/>
-    </row>
-    <row r="73" ht="13.5" customHeight="1">
-      <c r="B73" s="1"/>
-      <c r="C73" s="1"/>
-      <c r="I73" s="1"/>
-    </row>
-    <row r="74" ht="13.5" customHeight="1">
-      <c r="B74" s="1"/>
+      <c r="I72" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" ht="30.6" customHeight="1">
+      <c r="B73" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I73" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A74" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>90</v>
+      </c>
       <c r="C74" s="1"/>
-      <c r="I74" s="1"/>
-    </row>
-    <row r="75" ht="13.5" customHeight="1">
+      <c r="I74" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A75" s="1" t="s">
+        <v>90</v>
+      </c>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
       <c r="I75" s="1"/>
     </row>
-    <row r="76" ht="13.5" customHeight="1">
-      <c r="B76" s="1"/>
-      <c r="C76" s="1"/>
-      <c r="I76" s="1"/>
-    </row>
-    <row r="77" ht="13.5" customHeight="1">
-      <c r="B77" s="1"/>
-      <c r="C77" s="1"/>
-      <c r="I77" s="1"/>
-    </row>
-    <row r="78" ht="13.5" customHeight="1">
-      <c r="B78" s="1"/>
+    <row r="76" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B76" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I76" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" ht="30.6" customHeight="1">
+      <c r="B77" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I77" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A78" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>94</v>
+      </c>
       <c r="C78" s="1"/>
-      <c r="I78" s="1"/>
-      <c r="J78" s="1"/>
-    </row>
-    <row r="79" ht="13.5" customHeight="1">
+      <c r="I78" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A79" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B79" s="1"/>
+      <c r="C79" s="1"/>
       <c r="I79" s="1"/>
     </row>
-    <row r="80" ht="13.5" customHeight="1">
-      <c r="I80" s="1"/>
-    </row>
-    <row r="81" ht="13.5" customHeight="1">
-      <c r="I81" s="1"/>
-    </row>
-    <row r="82" ht="13.5" customHeight="1">
-      <c r="A82" s="1"/>
-      <c r="B82" s="1"/>
+    <row r="80" spans="1:10" ht="30.6" customHeight="1">
+      <c r="B80" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I80" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="J80" s="1"/>
+    </row>
+    <row r="81" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A81" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I81" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A82" s="1" t="s">
+        <v>97</v>
+      </c>
       <c r="I82" s="1"/>
-      <c r="J82" s="1"/>
-    </row>
-    <row r="83" ht="13.5" customHeight="1">
-      <c r="A83" s="1"/>
-      <c r="B83" s="1"/>
+    </row>
+    <row r="83" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A83" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B83" s="9" t="s">
+        <v>103</v>
+      </c>
       <c r="I83" s="1"/>
-      <c r="J83" s="1"/>
-    </row>
-    <row r="84" ht="13.5" customHeight="1">
-      <c r="A84" s="1"/>
-    </row>
-    <row r="85" ht="13.5" customHeight="1">
-      <c r="B85" s="1"/>
-      <c r="C85" s="1"/>
-      <c r="I85" s="1"/>
-    </row>
-    <row r="86" ht="13.5" customHeight="1">
-      <c r="B86" s="1"/>
-      <c r="C86" s="1"/>
-      <c r="I86" s="1"/>
-    </row>
-    <row r="87" ht="13.5" customHeight="1">
-      <c r="B87" s="1"/>
-      <c r="C87" s="1"/>
-      <c r="I87" s="1"/>
-    </row>
-    <row r="88" ht="13.5" customHeight="1">
+    </row>
+    <row r="84" spans="1:10" ht="30.6" customHeight="1">
+      <c r="B84" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I84" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" ht="30" customHeight="1">
+      <c r="A85" s="1"/>
+      <c r="B85" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C85" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I85" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="J85" s="1"/>
+    </row>
+    <row r="86" spans="1:10" ht="30" customHeight="1">
+      <c r="A86" s="1"/>
+      <c r="B86" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I86" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="J86" s="1"/>
+    </row>
+    <row r="87" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A87" s="1"/>
+      <c r="B87" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I87" s="12" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="30" customHeight="1">
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
-      <c r="I88" s="1"/>
-    </row>
-    <row r="89" ht="13.5" customHeight="1">
-      <c r="A89" s="1"/>
+      <c r="I88" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" ht="30.6" customHeight="1">
       <c r="B89" s="1"/>
-    </row>
-    <row r="90" ht="13.5" customHeight="1">
-      <c r="A90" s="1"/>
-    </row>
-    <row r="91" ht="13.5" customHeight="1">
-      <c r="B91" s="1"/>
+      <c r="C89" s="1"/>
+      <c r="I89" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="30" customHeight="1">
+      <c r="B90" s="1"/>
+      <c r="C90" s="1"/>
+      <c r="I90" s="5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A91" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>107</v>
+      </c>
       <c r="C91" s="1"/>
-      <c r="I91" s="1"/>
-    </row>
-    <row r="92" ht="13.5" customHeight="1">
-      <c r="B92" s="1"/>
-      <c r="C92" s="1"/>
-      <c r="I92" s="1"/>
-    </row>
-    <row r="93" ht="13.5" customHeight="1">
-      <c r="B93" s="1"/>
-      <c r="C93" s="1"/>
-      <c r="I93" s="1"/>
-    </row>
-    <row r="94" ht="13.5" customHeight="1">
-      <c r="B94" s="1"/>
-      <c r="C94" s="1"/>
-      <c r="I94" s="1"/>
-    </row>
-    <row r="95" ht="13.5" customHeight="1">
-      <c r="A95" s="1"/>
-      <c r="B95" s="1"/>
-    </row>
-    <row r="96" ht="13.5" customHeight="1">
-      <c r="A96" s="1"/>
-    </row>
-    <row r="97" ht="13.5" customHeight="1">
+      <c r="I91" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A92" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="I92" s="5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A93" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="30" customHeight="1">
+      <c r="B94" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C94" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I94" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" ht="30.6" customHeight="1">
+      <c r="B95" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I95" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B96" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C96" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I96" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A97" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B97" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="C97" s="1"/>
       <c r="I97" s="1"/>
     </row>
-    <row r="98" ht="13.5" customHeight="1">
-      <c r="I98" s="1"/>
-    </row>
-    <row r="99" ht="13.5" customHeight="1">
+    <row r="98" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A98" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B98" s="1"/>
+    </row>
+    <row r="99" spans="1:9" ht="13.5" customHeight="1">
       <c r="A99" s="1"/>
-      <c r="B99" s="1"/>
-      <c r="I99" s="1"/>
-    </row>
-    <row r="100" ht="13.5" customHeight="1">
-      <c r="A100" s="1"/>
-      <c r="H100" s="1"/>
-      <c r="I100" s="1"/>
-    </row>
-    <row r="101" ht="13.5" customHeight="1">
-      <c r="B101" s="1"/>
-      <c r="C101" s="1"/>
-      <c r="I101" s="1"/>
-    </row>
-    <row r="102" ht="13.5" customHeight="1">
-      <c r="B102" s="1"/>
-      <c r="C102" s="1"/>
+      <c r="B99" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I99" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B100" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I100" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="30" customHeight="1">
+      <c r="B101" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I101" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A102" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B102" s="11" t="s">
+        <v>114</v>
+      </c>
       <c r="I102" s="1"/>
     </row>
-    <row r="103" ht="13.5" customHeight="1">
-      <c r="B103" s="1"/>
-      <c r="C103" s="1"/>
+    <row r="103" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A103" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="H103" s="1"/>
       <c r="I103" s="1"/>
     </row>
-    <row r="104" ht="13.5" customHeight="1">
-      <c r="I104" s="1"/>
-    </row>
-    <row r="105" ht="13.5" customHeight="1">
-      <c r="I105" s="1"/>
-    </row>
-    <row r="106" ht="13.5" customHeight="1">
-      <c r="I106" s="1"/>
-    </row>
-    <row r="107" ht="13.5" customHeight="1">
-      <c r="I107" s="1"/>
-    </row>
-    <row r="108" ht="13.5" customHeight="1">
-      <c r="B108" s="1"/>
-      <c r="C108" s="1"/>
-      <c r="I108" s="1"/>
-    </row>
-    <row r="109" ht="13.5" customHeight="1">
-      <c r="B109" s="1"/>
-      <c r="C109" s="1"/>
+    <row r="104" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B104" s="1"/>
+      <c r="C104" s="1"/>
+      <c r="I104" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B105" s="1"/>
+      <c r="C105" s="1"/>
+      <c r="I105" s="5" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B106" s="1"/>
+      <c r="C106" s="1"/>
+      <c r="I106" s="5" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" ht="28.8" customHeight="1">
+      <c r="I107" s="5" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A108" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="I108" s="5" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A109" s="1" t="s">
+        <v>122</v>
+      </c>
       <c r="I109" s="1"/>
     </row>
-    <row r="110" ht="13.5" customHeight="1">
-      <c r="B110" s="1"/>
-      <c r="C110" s="1"/>
-      <c r="I110" s="1"/>
-    </row>
-    <row r="111" ht="13.5" customHeight="1">
-      <c r="B111" s="1"/>
-      <c r="C111" s="1"/>
-      <c r="I111" s="1"/>
-    </row>
-    <row r="112" ht="13.5" customHeight="1">
-      <c r="B112" s="1"/>
-      <c r="C112" s="1"/>
-      <c r="I112" s="1"/>
-    </row>
-    <row r="113" ht="13.5" customHeight="1">
-      <c r="A113" s="1"/>
-      <c r="B113" s="1"/>
-      <c r="I113" s="1"/>
-      <c r="J113" s="1"/>
-    </row>
-    <row r="114" ht="13.5" customHeight="1">
-      <c r="A114" s="1"/>
-      <c r="B114" s="1"/>
-      <c r="I114" s="1"/>
-      <c r="J114" s="1"/>
-    </row>
-    <row r="115" ht="13.5" customHeight="1">
-      <c r="A115" s="1"/>
-      <c r="I115" s="1"/>
-      <c r="J115" s="1"/>
-    </row>
-    <row r="116" ht="13.5" customHeight="1">
-      <c r="B116" s="1"/>
+    <row r="110" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B110" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C110" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I110" s="5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B111" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C111" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I111" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="30" customHeight="1">
+      <c r="B112" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C112" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I112" s="5" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A113" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C113" s="1"/>
+      <c r="I113" s="5" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A114" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C114" s="1"/>
+      <c r="I114" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A115" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B115" s="1"/>
+      <c r="C115" s="1"/>
+      <c r="I115" s="5"/>
+    </row>
+    <row r="116" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A116" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B116" s="11" t="s">
+        <v>131</v>
+      </c>
       <c r="C116" s="1"/>
       <c r="I116" s="1"/>
     </row>
-    <row r="117" ht="13.5" customHeight="1">
-      <c r="A117" s="1"/>
+    <row r="117" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A117" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="B117" s="1"/>
-    </row>
-    <row r="118" ht="13.5" customHeight="1">
-      <c r="A118" s="1"/>
-    </row>
-    <row r="119" ht="13.5" customHeight="1">
-      <c r="B119" s="1"/>
-      <c r="C119" s="1"/>
+      <c r="I117" s="1"/>
+      <c r="J117" s="1"/>
+    </row>
+    <row r="118" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A118" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B118" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="I118" s="1"/>
+      <c r="J118" s="1"/>
+    </row>
+    <row r="119" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A119" s="11" t="s">
+        <v>131</v>
+      </c>
       <c r="I119" s="1"/>
-    </row>
-    <row r="120" ht="13.5" customHeight="1">
-      <c r="B120" s="1"/>
-      <c r="C120" s="1"/>
-      <c r="I120" s="1"/>
-    </row>
-    <row r="121" ht="13.5" customHeight="1">
-      <c r="B121" s="1"/>
-      <c r="C121" s="1"/>
-      <c r="I121" s="1"/>
-    </row>
-    <row r="122" ht="13.5" customHeight="1">
-      <c r="A122" s="1"/>
-      <c r="B122" s="1"/>
-    </row>
-    <row r="123" ht="13.5" customHeight="1">
-      <c r="A123" s="1"/>
-      <c r="B123" s="1"/>
-      <c r="I123" s="1"/>
-      <c r="J123" s="1"/>
-    </row>
-    <row r="124" ht="13.5" customHeight="1">
-      <c r="B124" s="1"/>
-      <c r="C124" s="1"/>
-      <c r="I124" s="1"/>
-    </row>
-    <row r="125" ht="13.5" customHeight="1">
-      <c r="B125" s="1"/>
-      <c r="C125" s="1"/>
-      <c r="I125" s="1"/>
-    </row>
-    <row r="126" ht="13.5" customHeight="1">
+      <c r="J119" s="1"/>
+    </row>
+    <row r="120" spans="1:10" ht="30.6" customHeight="1">
+      <c r="B120" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C120" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I120" s="5" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A121" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="I121" s="9" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A122" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B123" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C123" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I123" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B124" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C124" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I124" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" ht="30" customHeight="1">
+      <c r="B125" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C125" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I125" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" ht="13.5" customHeight="1">
       <c r="A126" s="1"/>
-      <c r="B126" s="1"/>
-    </row>
-    <row r="127" ht="13.5" customHeight="1">
+      <c r="B126" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C126" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I126" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" ht="28.8" customHeight="1">
       <c r="A127" s="1"/>
-    </row>
-    <row r="128" ht="13.5" customHeight="1">
-      <c r="I128" s="1"/>
-    </row>
-    <row r="129" ht="13.5" customHeight="1">
-      <c r="A129" s="1"/>
-    </row>
-    <row r="130" ht="13.5" customHeight="1">
-      <c r="A130" s="1"/>
-    </row>
-    <row r="131" ht="13.5" customHeight="1">
+      <c r="B127" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C127" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I127" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="J127" s="1"/>
+    </row>
+    <row r="128" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A128" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C128" s="1"/>
+      <c r="I128" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A129" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C129" s="1"/>
+      <c r="I129" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A130" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B130" s="1"/>
+    </row>
+    <row r="131" spans="1:9" ht="13.5" customHeight="1">
       <c r="A131" s="1"/>
-      <c r="B131" s="1"/>
-      <c r="H131" s="1"/>
-      <c r="I131" s="1"/>
-    </row>
-    <row r="132" ht="13.5" customHeight="1">
-      <c r="A132" s="1"/>
-      <c r="H132" s="1"/>
-      <c r="I132" s="1"/>
-    </row>
-    <row r="133" ht="13.5" customHeight="1">
-      <c r="I133" s="1"/>
-    </row>
-    <row r="134" ht="13.5" customHeight="1">
-      <c r="I134" s="1"/>
-    </row>
-    <row r="135" ht="13.5" customHeight="1">
-      <c r="I135" s="1"/>
-    </row>
-    <row r="136" ht="13.5" customHeight="1">
-      <c r="I136" s="1"/>
-    </row>
-    <row r="137" ht="13.5" customHeight="1">
-      <c r="I137" s="1"/>
-    </row>
-    <row r="138" ht="13.5" customHeight="1">
+      <c r="B131" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C131" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I131" s="9" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" ht="28.2" customHeight="1">
+      <c r="B132" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C132" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I132" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A133" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B133" s="11" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A134" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" ht="27.6" customHeight="1">
+      <c r="A135" s="1"/>
+      <c r="B135" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C135" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H135" s="1"/>
+      <c r="I135" s="5" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" ht="30.6" customHeight="1">
+      <c r="A136" s="1"/>
+      <c r="B136" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C136" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H136" s="1"/>
+      <c r="I136" s="5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B137" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C137" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I137" s="5" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A138" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B138" s="11" t="s">
+        <v>146</v>
+      </c>
       <c r="I138" s="1"/>
     </row>
-    <row r="139" ht="13.5" customHeight="1">
+    <row r="139" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A139" s="11" t="s">
+        <v>146</v>
+      </c>
       <c r="I139" s="1"/>
     </row>
-    <row r="140" ht="13.5" customHeight="1"/>
-    <row r="141" ht="13.5" customHeight="1"/>
-    <row r="142" ht="13.5" customHeight="1"/>
-    <row r="143" ht="13.5" customHeight="1"/>
-    <row r="144" ht="13.5" customHeight="1"/>
-    <row r="145" ht="13.5" customHeight="1"/>
-    <row r="146" ht="13.5" customHeight="1"/>
-    <row r="147" ht="13.5" customHeight="1"/>
-    <row r="148" ht="13.5" customHeight="1"/>
-    <row r="149" ht="13.5" customHeight="1"/>
-    <row r="150" ht="13.5" customHeight="1"/>
-    <row r="151" ht="13.5" customHeight="1"/>
-    <row r="152" ht="13.5" customHeight="1"/>
-    <row r="153" ht="13.5" customHeight="1"/>
-    <row r="154" ht="13.5" customHeight="1"/>
-    <row r="155" ht="13.5" customHeight="1"/>
-    <row r="156" ht="13.5" customHeight="1"/>
-    <row r="157" ht="13.5" customHeight="1"/>
-    <row r="158" ht="13.5" customHeight="1"/>
-    <row r="159" ht="13.5" customHeight="1"/>
-    <row r="160" ht="13.5" customHeight="1"/>
+    <row r="140" spans="1:9" ht="30" customHeight="1">
+      <c r="B140" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C140" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I140" s="5" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" ht="30" customHeight="1">
+      <c r="B141" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C141" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I141" s="5" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B142" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C142" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I142" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B143" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C143" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I143" s="5" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B144" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C144" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I144" s="5" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B145" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C145" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I145" s="12" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" ht="30" customHeight="1">
+      <c r="B146" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C146" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I146" s="12" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B147" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C147" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I147" s="12" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B148" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C148" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I148" s="12" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I149" s="12" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I150" s="12" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" ht="28.8" customHeight="1">
+      <c r="I151" s="12" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" ht="28.8" customHeight="1">
+      <c r="I152" s="12" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" ht="30.6" customHeight="1">
+      <c r="I153" s="12" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I154" s="12" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A155" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B155" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="C155" s="9"/>
+      <c r="I155" s="12"/>
+    </row>
+    <row r="156" spans="1:9" ht="30" customHeight="1">
+      <c r="A156" s="9"/>
+      <c r="I156" s="12" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" ht="30.6" customHeight="1">
+      <c r="I157" s="12" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="159" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="160" spans="1:9" ht="13.5" customHeight="1"/>
     <row r="161" ht="13.5" customHeight="1"/>
     <row r="162" ht="13.5" customHeight="1"/>
     <row r="163" ht="13.5" customHeight="1"/>
@@ -1123,22 +2623,29 @@
     <row r="206" ht="13.5" customHeight="1"/>
     <row r="207" ht="13.5" customHeight="1"/>
     <row r="208" ht="13.5" customHeight="1"/>
-    <row r="209" ht="13.5" customHeight="1"/>
-    <row r="210" ht="13.5" customHeight="1"/>
-    <row r="211" ht="13.5" customHeight="1"/>
-    <row r="212" ht="13.5" customHeight="1"/>
-    <row r="213" ht="13.5" customHeight="1"/>
-    <row r="214" ht="13.5" customHeight="1"/>
-    <row r="215" ht="13.5" customHeight="1"/>
-    <row r="216" ht="13.5" customHeight="1"/>
-    <row r="217" ht="13.5" customHeight="1"/>
-    <row r="218" ht="13.5" customHeight="1"/>
-    <row r="219" ht="13.5" customHeight="1"/>
-    <row r="220" ht="13.5" customHeight="1"/>
-    <row r="221" ht="13.5" customHeight="1"/>
-    <row r="222" ht="13.5" customHeight="1"/>
-    <row r="223" ht="13.5" customHeight="1"/>
-    <row r="224" ht="13.5" customHeight="1"/>
+    <row r="209" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="210" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="211" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="212" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="213" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="214" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="215" spans="1:2" ht="13.5" customHeight="1">
+      <c r="A215" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B215" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="217" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="218" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="219" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="220" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="221" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="222" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="223" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="224" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="225" ht="13.5" customHeight="1"/>
     <row r="226" ht="13.5" customHeight="1"/>
     <row r="227" ht="13.5" customHeight="1"/>
@@ -1973,10 +3480,14 @@
     <row r="1056" ht="13.5" customHeight="1"/>
     <row r="1057" ht="13.5" customHeight="1"/>
     <row r="1058" ht="13.5" customHeight="1"/>
+    <row r="1059" ht="13.5" customHeight="1"/>
+    <row r="1060" ht="13.5" customHeight="1"/>
+    <row r="1061" ht="13.5" customHeight="1"/>
+    <row r="1062" ht="13.5" customHeight="1"/>
+    <row r="1063" ht="13.5" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/test260903/chapter0106.xlsx
+++ b/Assets/test260903/chapter0106.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="412" documentId="11_AA3EC6FCFDC488042E83A027A8BF20349734F0B7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07B4D029-B20A-4E75-A3FB-6A1D8EFF5C95}"/>
+  <xr:revisionPtr revIDLastSave="467" documentId="11_AA3EC6FCFDC488042E83A027A8BF20349734F0B7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23FBF251-23DC-4C25-A702-336D6185B85A}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="183">
   <si>
     <t>Command</t>
   </si>
@@ -729,10 +729,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>不意に甘く爽やかな香りがした。</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>その香りは、有希の匂いだった。
 彼女の体が触れ合うほど近くに……</t>
     <phoneticPr fontId="3"/>
@@ -763,12 +759,75 @@
   </si>
   <si>
     <t>一枚絵</t>
-    <rPh sb="0" eb="2">
-      <t>イチマイ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>エ</t>
-    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>BgEvent</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>一秒、二秒、三秒……
+やがて、有希の唇が離れて行った</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>そして有希が、つぶっていた目を開け……</t>
+  </si>
+  <si>
+    <t>……えへっ♪
+これなら、忘れんちゃね</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>私もセンセーも、これならさっ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>有希が、笑顔を浮かべる。
+ほっぺは真っ赤だけど、満足そうに</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>……それを見て、僕はやっぱり確信した</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>これから先、上手くいくかは分からない。
+僕らの夢が叶う保証もない</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>また失敗をして、
+トボトボ帰ってくるかもしれない</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>でも、有希と……一番好きな人と、
+こうして笑い合っていると……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>やっぱり僕は思うんだ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>何がどうなろうと、後悔なんかしない。
+……絶対に</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>BgEventOff</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>&lt;Off&gt;</t>
+  </si>
+  <si>
+    <t>BgOff</t>
+  </si>
+  <si>
+    <t>不意に甘く爽やかな香りがした。
+有希が一歩前に出たのだ</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -1082,7 +1141,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1063"/>
+  <dimension ref="A1:L1066"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.44140625" customWidth="1"/>
@@ -1174,11 +1233,9 @@
     </row>
     <row r="5" spans="1:12" ht="13.5" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -1189,10 +1246,10 @@
     </row>
     <row r="6" spans="1:12" ht="13.5" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -1203,114 +1260,118 @@
       <c r="I6" s="1"/>
     </row>
     <row r="7" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A7" s="1"/>
-      <c r="B7" s="3"/>
+      <c r="A7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
+      <c r="H7" s="4"/>
       <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
     </row>
     <row r="8" spans="1:12" ht="13.5" customHeight="1">
-      <c r="B8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1" t="s">
+      <c r="A8" s="1"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+    </row>
+    <row r="9" spans="1:12" ht="13.5" customHeight="1">
+      <c r="B9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="K8" s="1"/>
-    </row>
-    <row r="9" spans="1:12" ht="28.8" customHeight="1">
-      <c r="H9" s="1"/>
-      <c r="I9" s="5" t="s">
+      <c r="K9" s="1"/>
+    </row>
+    <row r="10" spans="1:12" ht="28.8" customHeight="1">
+      <c r="H10" s="1"/>
+      <c r="I10" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="30.6" customHeight="1">
-      <c r="I10" s="6" t="s">
+    <row r="11" spans="1:12" ht="30.6" customHeight="1">
+      <c r="I11" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="28.8" customHeight="1">
-      <c r="I11" s="6" t="s">
+    <row r="12" spans="1:12" ht="28.8" customHeight="1">
+      <c r="I12" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="13.5" customHeight="1">
-      <c r="I12" s="1" t="s">
+    <row r="13" spans="1:12" ht="13.5" customHeight="1">
+      <c r="I13" s="1" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="28.8" customHeight="1">
-      <c r="I13" s="6" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="28.8" customHeight="1">
       <c r="I14" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="28.8" customHeight="1">
+      <c r="I15" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="J14" s="1"/>
-    </row>
-    <row r="15" spans="1:12" ht="30" customHeight="1">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="I15" s="6" t="s">
-        <v>29</v>
-      </c>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" spans="1:12" ht="30.6" customHeight="1">
+    <row r="16" spans="1:12" ht="30" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
+      <c r="G16" s="1"/>
       <c r="I16" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" spans="1:10" ht="30" customHeight="1">
+    <row r="17" spans="1:10" ht="30.6" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="I17" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" spans="1:10" ht="13.5" customHeight="1">
+    <row r="18" spans="1:10" ht="30" customHeight="1">
+      <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
-      <c r="I18" s="1" t="s">
+      <c r="I18" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J18" s="1"/>
+    </row>
+    <row r="19" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="I19" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J18" s="1"/>
-    </row>
-    <row r="19" spans="1:10" ht="28.8" customHeight="1">
-      <c r="A19" s="1"/>
-      <c r="B19" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I19" s="6" t="s">
+      <c r="J19" s="1"/>
+    </row>
+    <row r="20" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A20" s="1"/>
+      <c r="B20" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I20" s="6" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A20" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="13.5" customHeight="1">
@@ -1318,68 +1379,68 @@
         <v>36</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A22" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="I21" s="6" t="s">
+      <c r="I22" s="6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A22" s="1" t="s">
+    <row r="23" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A23" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-    </row>
-    <row r="23" spans="1:10" ht="16.2" customHeight="1">
-      <c r="B23" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I23" s="10" t="s">
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+    </row>
+    <row r="24" spans="1:10" ht="16.2" customHeight="1">
+      <c r="B24" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I24" s="10" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="30" customHeight="1">
-      <c r="B24" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I24" s="6" t="s">
+    <row r="25" spans="1:10" ht="30" customHeight="1">
+      <c r="B25" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I25" s="6" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A25" s="9" t="s">
+    <row r="26" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A26" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B26" s="11" t="s">
         <v>44</v>
-      </c>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-    </row>
-    <row r="26" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A26" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
     </row>
-    <row r="27" spans="1:10" ht="30" customHeight="1">
-      <c r="B27" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>45</v>
-      </c>
+    <row r="27" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A27" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
     </row>
     <row r="28" spans="1:10" ht="30" customHeight="1">
       <c r="B28" s="7" t="s">
@@ -1389,163 +1450,162 @@
         <v>35</v>
       </c>
       <c r="I28" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="30" customHeight="1">
+      <c r="B29" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I29" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A29" s="1" t="s">
+    <row r="30" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A30" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B29" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-    </row>
-    <row r="30" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A30" s="11" t="s">
+      <c r="B30" s="11" t="s">
         <v>44</v>
       </c>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
     </row>
     <row r="31" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I31" s="1" t="s">
+      <c r="A31" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+    </row>
+    <row r="32" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I32" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="28.8" customHeight="1">
-      <c r="I32" s="5" t="s">
+    <row r="33" spans="1:9" ht="28.8" customHeight="1">
+      <c r="I33" s="5" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="28.8" customHeight="1">
-      <c r="I33" s="5" t="s">
+    <row r="34" spans="1:9" ht="28.8" customHeight="1">
+      <c r="I34" s="5" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="28.8" customHeight="1">
-      <c r="I34" s="5" t="s">
+    <row r="35" spans="1:9" ht="28.8" customHeight="1">
+      <c r="I35" s="5" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="30.6" customHeight="1">
-      <c r="I35" s="5" t="s">
+    <row r="36" spans="1:9" ht="30.6" customHeight="1">
+      <c r="I36" s="5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="30" customHeight="1">
-      <c r="I36" s="5" t="s">
+    <row r="37" spans="1:9" ht="30" customHeight="1">
+      <c r="I37" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="30" customHeight="1">
-      <c r="B37" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I37" s="5" t="s">
+    <row r="38" spans="1:9" ht="30" customHeight="1">
+      <c r="B38" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I38" s="5" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="30.6" customHeight="1">
-      <c r="B38" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I38" s="5" t="s">
+    <row r="39" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B39" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I39" s="5" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="28.2" customHeight="1">
-      <c r="B39" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I39" s="5" t="s">
+    <row r="40" spans="1:9" ht="28.2" customHeight="1">
+      <c r="B40" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I40" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B40" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I40" s="6" t="s">
+    <row r="41" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B41" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I41" s="6" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A41" s="9" t="s">
+    <row r="42" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A42" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B42" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I41" s="5" t="s">
+      <c r="I42" s="5" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A42" s="1" t="s">
+    <row r="43" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A43" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I42" s="1"/>
-    </row>
-    <row r="43" spans="1:10" ht="31.2" customHeight="1">
-      <c r="B43" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I43" s="5" t="s">
+      <c r="I43" s="1"/>
+    </row>
+    <row r="44" spans="1:9" ht="31.2" customHeight="1">
+      <c r="B44" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I44" s="5" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B44" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I44" s="5" t="s">
+    <row r="45" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B45" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I45" s="5" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B45" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I45" s="5" t="s">
+    <row r="46" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B46" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I46" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A46" s="1"/>
-      <c r="B46" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I46" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="30" customHeight="1">
+    <row r="47" spans="1:9" ht="13.5" customHeight="1">
       <c r="A47" s="1"/>
       <c r="B47" s="7" t="s">
         <v>34</v>
@@ -1554,81 +1614,81 @@
         <v>35</v>
       </c>
       <c r="I47" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="30" customHeight="1">
+      <c r="A48" s="1"/>
+      <c r="B48" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I48" s="5" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="30.6" customHeight="1">
-      <c r="A48" s="1"/>
-      <c r="I48" s="5" t="s">
+    <row r="49" spans="1:10" ht="30.6" customHeight="1">
+      <c r="A49" s="1"/>
+      <c r="I49" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="J48" s="1"/>
-    </row>
-    <row r="49" spans="1:10" ht="30" customHeight="1">
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
-      <c r="I49" s="5" t="s">
-        <v>65</v>
-      </c>
+      <c r="J49" s="1"/>
     </row>
     <row r="50" spans="1:10" ht="30" customHeight="1">
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="I50" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="J50" s="1"/>
+        <v>65</v>
+      </c>
     </row>
     <row r="51" spans="1:10" ht="30" customHeight="1">
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="I51" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="J51" s="1"/>
+    </row>
+    <row r="52" spans="1:10" ht="30" customHeight="1">
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="I52" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="J51" s="1"/>
-    </row>
-    <row r="52" spans="1:10" ht="28.8" customHeight="1">
-      <c r="A52" s="1"/>
-      <c r="B52" s="1"/>
-      <c r="I52" s="5" t="s">
+      <c r="J52" s="1"/>
+    </row>
+    <row r="53" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A53" s="1"/>
+      <c r="B53" s="1"/>
+      <c r="I53" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="J52" s="1"/>
-    </row>
-    <row r="53" spans="1:10" ht="30" customHeight="1">
-      <c r="A53" s="1"/>
-      <c r="I53" s="5" t="s">
+      <c r="J53" s="1"/>
+    </row>
+    <row r="54" spans="1:10" ht="30" customHeight="1">
+      <c r="A54" s="1"/>
+      <c r="I54" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="J53" s="1"/>
-    </row>
-    <row r="54" spans="1:10" ht="30" customHeight="1">
-      <c r="B54" s="1"/>
-      <c r="C54" s="1"/>
-      <c r="I54" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="31.2" customHeight="1">
+      <c r="J54" s="1"/>
+    </row>
+    <row r="55" spans="1:10" ht="30" customHeight="1">
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
       <c r="I55" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="31.2" customHeight="1">
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="I56" s="5" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="31.2" customHeight="1">
-      <c r="A56" s="1"/>
-      <c r="B56" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I56" s="5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="28.8" customHeight="1">
+    <row r="57" spans="1:10" ht="31.2" customHeight="1">
       <c r="A57" s="1"/>
       <c r="B57" s="7" t="s">
         <v>34</v>
@@ -1637,271 +1697,270 @@
         <v>35</v>
       </c>
       <c r="I57" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A58" s="1"/>
+      <c r="B58" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I58" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A58" s="9" t="s">
+    <row r="59" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A59" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B59" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="I58" s="5" t="s">
+      <c r="I59" s="5" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A59" s="1" t="s">
+    <row r="60" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A60" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="I59" s="1"/>
-    </row>
-    <row r="60" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A60" s="1"/>
-      <c r="B60" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C60" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I60" s="5" t="s">
+      <c r="I60" s="1"/>
+    </row>
+    <row r="61" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A61" s="1"/>
+      <c r="B61" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I61" s="5" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="28.8" customHeight="1">
-      <c r="A61" s="1"/>
-      <c r="B61" s="1"/>
-      <c r="I61" s="5" t="s">
+    <row r="62" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A62" s="1"/>
+      <c r="B62" s="1"/>
+      <c r="I62" s="5" t="s">
         <v>77</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="30" customHeight="1">
-      <c r="B62" s="1"/>
-      <c r="C62" s="1"/>
-      <c r="I62" s="5" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="30" customHeight="1">
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="I63" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="30" customHeight="1">
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
       <c r="I64" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" ht="30" customHeight="1">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="30" customHeight="1">
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
       <c r="I65" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="30" customHeight="1">
+      <c r="B66" s="1"/>
+      <c r="C66" s="1"/>
+      <c r="I66" s="5" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A66" s="1"/>
-      <c r="B66" s="1"/>
-      <c r="I66" s="5" t="s">
+    <row r="67" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A67" s="1"/>
+      <c r="B67" s="1"/>
+      <c r="I67" s="5" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="30" customHeight="1">
-      <c r="A67" s="1"/>
-      <c r="B67" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C67" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H67" s="1"/>
-      <c r="I67" s="5" t="s">
+    <row r="68" spans="1:9" ht="30" customHeight="1">
+      <c r="A68" s="1"/>
+      <c r="B68" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H68" s="1"/>
+      <c r="I68" s="5" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B68" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I68" s="5" t="s">
+    <row r="69" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B69" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I69" s="5" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B69" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I69" s="5" t="s">
+    <row r="70" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B70" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I70" s="5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="28.8" customHeight="1">
-      <c r="A70" s="1"/>
-      <c r="B70" s="1"/>
-      <c r="I70" s="5" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" ht="13.5" customHeight="1">
+    <row r="71" spans="1:9" ht="28.8" customHeight="1">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
-      <c r="H71" s="1"/>
-      <c r="I71" s="1" t="s">
+      <c r="I71" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A72" s="1"/>
+      <c r="B72" s="1"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B72" s="1"/>
-      <c r="C72" s="1"/>
-      <c r="I72" s="5" t="s">
+    <row r="73" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B73" s="1"/>
+      <c r="C73" s="1"/>
+      <c r="I73" s="5" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="30.6" customHeight="1">
-      <c r="B73" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I73" s="5" t="s">
+    <row r="74" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B74" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I74" s="5" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A74" s="9" t="s">
+    <row r="75" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A75" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B75" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C74" s="1"/>
-      <c r="I74" s="5" t="s">
+      <c r="C75" s="1"/>
+      <c r="I75" s="5" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A75" s="1" t="s">
+    <row r="76" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A76" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B75" s="1"/>
-      <c r="C75" s="1"/>
-      <c r="I75" s="1"/>
-    </row>
-    <row r="76" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B76" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I76" s="5" t="s">
+      <c r="B76" s="1"/>
+      <c r="C76" s="1"/>
+      <c r="I76" s="1"/>
+    </row>
+    <row r="77" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B77" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I77" s="5" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="30.6" customHeight="1">
-      <c r="B77" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I77" s="5" t="s">
+    <row r="78" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B78" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I78" s="5" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A78" s="9" t="s">
+    <row r="79" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A79" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="B79" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C78" s="1"/>
-      <c r="I78" s="1" t="s">
+      <c r="C79" s="1"/>
+      <c r="I79" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A79" s="1" t="s">
+    <row r="80" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A80" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B79" s="1"/>
-      <c r="C79" s="1"/>
-      <c r="I79" s="1"/>
-    </row>
-    <row r="80" spans="1:10" ht="30.6" customHeight="1">
-      <c r="B80" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C80" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I80" s="5" t="s">
+      <c r="B80" s="1"/>
+      <c r="C80" s="1"/>
+      <c r="I80" s="1"/>
+    </row>
+    <row r="81" spans="1:10" ht="30.6" customHeight="1">
+      <c r="B81" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I81" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="J80" s="1"/>
-    </row>
-    <row r="81" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A81" s="9" t="s">
+      <c r="J81" s="1"/>
+    </row>
+    <row r="82" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A82" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="B82" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="I81" s="5" t="s">
+      <c r="I82" s="5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="82" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A82" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="I82" s="1"/>
     </row>
     <row r="83" spans="1:10" ht="13.5" customHeight="1">
       <c r="A83" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I83" s="1"/>
+    </row>
+    <row r="84" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A84" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B83" s="9" t="s">
+      <c r="B84" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="I83" s="1"/>
-    </row>
-    <row r="84" spans="1:10" ht="30.6" customHeight="1">
-      <c r="B84" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C84" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I84" s="5" t="s">
+      <c r="I84" s="1"/>
+    </row>
+    <row r="85" spans="1:10" ht="30.6" customHeight="1">
+      <c r="B85" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C85" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I85" s="5" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="85" spans="1:10" ht="30" customHeight="1">
-      <c r="A85" s="1"/>
-      <c r="B85" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C85" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I85" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="J85" s="1"/>
     </row>
     <row r="86" spans="1:10" ht="30" customHeight="1">
       <c r="A86" s="1"/>
@@ -1912,11 +1971,11 @@
         <v>35</v>
       </c>
       <c r="I86" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J86" s="1"/>
     </row>
-    <row r="87" spans="1:10" ht="28.2" customHeight="1">
+    <row r="87" spans="1:10" ht="30" customHeight="1">
       <c r="A87" s="1"/>
       <c r="B87" s="7" t="s">
         <v>34</v>
@@ -1924,41 +1983,54 @@
       <c r="C87" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="I87" s="12" t="s">
+      <c r="I87" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="J87" s="1"/>
+    </row>
+    <row r="88" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A88" s="1"/>
+      <c r="B88" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C88" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I88" s="12" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="88" spans="1:10" ht="30" customHeight="1">
-      <c r="B88" s="1"/>
-      <c r="C88" s="1"/>
-      <c r="I88" s="5" t="s">
+    <row r="89" spans="1:10" ht="30" customHeight="1">
+      <c r="B89" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C89" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I89" s="5" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="30.6" customHeight="1">
-      <c r="B89" s="1"/>
-      <c r="C89" s="1"/>
-      <c r="I89" s="5" t="s">
+    <row r="90" spans="1:10" ht="30.6" customHeight="1">
+      <c r="B90" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C90" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I90" s="5" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="30" customHeight="1">
-      <c r="B90" s="1"/>
-      <c r="C90" s="1"/>
-      <c r="I90" s="5" t="s">
+    <row r="91" spans="1:10" ht="30" customHeight="1">
+      <c r="B91" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C91" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I91" s="5" t="s">
         <v>106</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A91" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C91" s="1"/>
-      <c r="I91" s="5" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="92" spans="1:10" ht="13.5" customHeight="1">
@@ -1966,169 +2038,170 @@
         <v>36</v>
       </c>
       <c r="B92" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C92" s="1"/>
+      <c r="I92" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A93" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="I92" s="5" t="s">
+      <c r="I93" s="5" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A93" s="1" t="s">
+    <row r="94" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A94" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="30" customHeight="1">
-      <c r="B94" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C94" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I94" s="5" t="s">
+    <row r="95" spans="1:10" ht="30" customHeight="1">
+      <c r="B95" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I95" s="5" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="30.6" customHeight="1">
-      <c r="B95" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C95" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I95" s="5" t="s">
+    <row r="96" spans="1:10" ht="30.6" customHeight="1">
+      <c r="B96" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C96" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I96" s="5" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B96" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C96" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I96" s="5" t="s">
+    <row r="97" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B97" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C97" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I97" s="5" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A97" s="9" t="s">
+    <row r="98" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A98" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B97" s="11" t="s">
+      <c r="B98" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="C97" s="1"/>
-      <c r="I97" s="1"/>
-    </row>
-    <row r="98" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A98" s="1" t="s">
+      <c r="C98" s="1"/>
+      <c r="I98" s="1"/>
+    </row>
+    <row r="99" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A99" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B98" s="1"/>
-    </row>
-    <row r="99" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A99" s="1"/>
-      <c r="B99" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C99" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I99" s="5" t="s">
+      <c r="B99" s="1"/>
+    </row>
+    <row r="100" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A100" s="1"/>
+      <c r="B100" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I100" s="5" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="30.6" customHeight="1">
-      <c r="B100" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C100" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I100" s="5" t="s">
+    <row r="101" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B101" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I101" s="5" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="30" customHeight="1">
-      <c r="B101" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C101" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I101" s="5" t="s">
+    <row r="102" spans="1:9" ht="30" customHeight="1">
+      <c r="B102" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C102" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I102" s="5" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A102" s="9" t="s">
+    <row r="103" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A103" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B102" s="11" t="s">
+      <c r="B103" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="I102" s="1"/>
-    </row>
-    <row r="103" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A103" s="11" t="s">
+      <c r="I103" s="1"/>
+    </row>
+    <row r="104" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A104" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="H103" s="1"/>
-      <c r="I103" s="1"/>
-    </row>
-    <row r="104" spans="1:9" ht="28.8" customHeight="1">
-      <c r="B104" s="1"/>
-      <c r="C104" s="1"/>
-      <c r="I104" s="5" t="s">
-        <v>118</v>
-      </c>
+      <c r="H104" s="1"/>
+      <c r="I104" s="1"/>
     </row>
     <row r="105" spans="1:9" ht="28.8" customHeight="1">
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
       <c r="I105" s="5" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" ht="13.5" customHeight="1">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="28.8" customHeight="1">
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
       <c r="I106" s="5" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B107" s="1"/>
+      <c r="C107" s="1"/>
+      <c r="I107" s="5" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="28.8" customHeight="1">
-      <c r="I107" s="5" t="s">
+    <row r="108" spans="1:9" ht="28.8" customHeight="1">
+      <c r="I108" s="5" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A108" s="9" t="s">
+    <row r="109" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A109" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B108" s="1" t="s">
+      <c r="B109" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="I108" s="5" t="s">
+      <c r="I109" s="5" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A109" s="1" t="s">
+    <row r="110" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A110" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="I109" s="1"/>
-    </row>
-    <row r="110" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B110" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C110" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I110" s="5" t="s">
-        <v>124</v>
-      </c>
+      <c r="I110" s="1"/>
     </row>
     <row r="111" spans="1:9" ht="13.5" customHeight="1">
       <c r="B111" s="7" t="s">
@@ -2138,30 +2211,29 @@
         <v>35</v>
       </c>
       <c r="I111" s="5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B112" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C112" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I112" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="30" customHeight="1">
-      <c r="B112" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C112" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I112" s="5" t="s">
+    <row r="113" spans="1:10" ht="30" customHeight="1">
+      <c r="B113" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C113" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I113" s="5" t="s">
         <v>126</v>
-      </c>
-    </row>
-    <row r="113" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A113" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C113" s="1"/>
-      <c r="I113" s="5" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="114" spans="1:10" ht="13.5" customHeight="1">
@@ -2169,92 +2241,93 @@
         <v>36</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C114" s="1"/>
       <c r="I114" s="5" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A115" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C115" s="1"/>
+      <c r="I115" s="5" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="115" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A115" s="1" t="s">
+    <row r="116" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A116" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B115" s="1"/>
-      <c r="C115" s="1"/>
-      <c r="I115" s="5"/>
-    </row>
-    <row r="116" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A116" s="9" t="s">
+      <c r="B116" s="1"/>
+      <c r="C116" s="1"/>
+      <c r="I116" s="5"/>
+    </row>
+    <row r="117" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A117" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B116" s="11" t="s">
+      <c r="B117" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="C116" s="1"/>
-      <c r="I116" s="1"/>
-    </row>
-    <row r="117" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A117" s="1" t="s">
+      <c r="C117" s="1"/>
+      <c r="I117" s="1"/>
+    </row>
+    <row r="118" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A118" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B117" s="1"/>
-      <c r="I117" s="1"/>
-      <c r="J117" s="1"/>
-    </row>
-    <row r="118" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A118" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="B118" s="11" t="s">
-        <v>131</v>
-      </c>
+      <c r="B118" s="1"/>
       <c r="I118" s="1"/>
       <c r="J118" s="1"/>
     </row>
     <row r="119" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A119" s="11" t="s">
+      <c r="A119" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B119" s="11" t="s">
         <v>131</v>
       </c>
       <c r="I119" s="1"/>
       <c r="J119" s="1"/>
     </row>
-    <row r="120" spans="1:10" ht="30.6" customHeight="1">
-      <c r="B120" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C120" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I120" s="5" t="s">
+    <row r="120" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A120" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="I120" s="1"/>
+      <c r="J120" s="1"/>
+    </row>
+    <row r="121" spans="1:10" ht="30.6" customHeight="1">
+      <c r="B121" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C121" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I121" s="5" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A121" s="9" t="s">
+    <row r="122" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A122" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="B122" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="I121" s="9" t="s">
+      <c r="I122" s="9" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="122" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A122" s="1" t="s">
+    <row r="123" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A123" s="1" t="s">
         <v>133</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B123" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C123" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I123" s="1" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="124" spans="1:10" ht="13.5" customHeight="1">
@@ -2265,33 +2338,32 @@
         <v>35</v>
       </c>
       <c r="I124" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B125" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C125" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I125" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="125" spans="1:10" ht="30" customHeight="1">
-      <c r="B125" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C125" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I125" s="5" t="s">
+    <row r="126" spans="1:10" ht="30" customHeight="1">
+      <c r="B126" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C126" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I126" s="5" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="126" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A126" s="1"/>
-      <c r="B126" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C126" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I126" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="127" spans="1:10" ht="28.8" customHeight="1">
+    <row r="127" spans="1:10" ht="13.5" customHeight="1">
       <c r="A127" s="1"/>
       <c r="B127" s="7" t="s">
         <v>34</v>
@@ -2299,91 +2371,90 @@
       <c r="C127" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="I127" s="5" t="s">
+      <c r="I127" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A128" s="1"/>
+      <c r="B128" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C128" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I128" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="J127" s="1"/>
-    </row>
-    <row r="128" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A128" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="C128" s="1"/>
-      <c r="I128" s="1" t="s">
-        <v>142</v>
-      </c>
+      <c r="J128" s="1"/>
     </row>
     <row r="129" spans="1:9" ht="13.5" customHeight="1">
       <c r="A129" s="9" t="s">
         <v>36</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C129" s="1"/>
       <c r="I129" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A130" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C130" s="1"/>
+      <c r="I130" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A130" s="1" t="s">
+    <row r="131" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A131" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B130" s="1"/>
-    </row>
-    <row r="131" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A131" s="1"/>
-      <c r="B131" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C131" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I131" s="9" t="s">
+      <c r="B131" s="1"/>
+    </row>
+    <row r="132" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A132" s="1"/>
+      <c r="B132" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C132" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I132" s="9" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="132" spans="1:9" ht="28.2" customHeight="1">
-      <c r="B132" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C132" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I132" s="5" t="s">
+    <row r="133" spans="1:9" ht="28.2" customHeight="1">
+      <c r="B133" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C133" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I133" s="5" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="133" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A133" s="9" t="s">
+    <row r="134" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A134" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B133" s="11" t="s">
+      <c r="B134" s="11" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="134" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A134" s="1" t="s">
+    <row r="135" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A135" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="135" spans="1:9" ht="27.6" customHeight="1">
-      <c r="A135" s="1"/>
-      <c r="B135" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C135" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H135" s="1"/>
-      <c r="I135" s="5" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="136" spans="1:9" ht="30.6" customHeight="1">
+    <row r="136" spans="1:9" ht="27.6" customHeight="1">
       <c r="A136" s="1"/>
       <c r="B136" s="7" t="s">
         <v>34</v>
@@ -2393,45 +2464,47 @@
       </c>
       <c r="H136" s="1"/>
       <c r="I136" s="5" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" ht="30.6" customHeight="1">
+      <c r="A137" s="1"/>
+      <c r="B137" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C137" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H137" s="1"/>
+      <c r="I137" s="5" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="137" spans="1:9" ht="30.6" customHeight="1">
-      <c r="B137" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C137" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I137" s="5" t="s">
+    <row r="138" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B138" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C138" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I138" s="5" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="138" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A138" s="9" t="s">
+    <row r="139" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A139" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B138" s="11" t="s">
+      <c r="B139" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="I138" s="1"/>
-    </row>
-    <row r="139" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A139" s="11" t="s">
+      <c r="I139" s="1"/>
+    </row>
+    <row r="140" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A140" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="I139" s="1"/>
-    </row>
-    <row r="140" spans="1:9" ht="30" customHeight="1">
-      <c r="B140" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C140" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I140" s="5" t="s">
-        <v>150</v>
-      </c>
+      <c r="I140" s="1"/>
     </row>
     <row r="141" spans="1:9" ht="30" customHeight="1">
       <c r="B141" s="7" t="s">
@@ -2441,18 +2514,18 @@
         <v>35</v>
       </c>
       <c r="I141" s="5" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" ht="30" customHeight="1">
+      <c r="B142" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C142" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I142" s="5" t="s">
         <v>151</v>
-      </c>
-    </row>
-    <row r="142" spans="1:9" ht="28.8" customHeight="1">
-      <c r="B142" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C142" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I142" s="5" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="143" spans="1:9" ht="28.8" customHeight="1">
@@ -2463,51 +2536,51 @@
         <v>35</v>
       </c>
       <c r="I143" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B144" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C144" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I144" s="5" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="144" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B144" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C144" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I144" s="5" t="s">
+    <row r="145" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B145" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C145" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I145" s="5" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="145" spans="1:9" ht="30.6" customHeight="1">
-      <c r="B145" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C145" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I145" s="12" t="s">
+    <row r="146" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B146" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C146" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I146" s="12" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="146" spans="1:9" ht="30" customHeight="1">
-      <c r="B146" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C146" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I146" s="12" t="s">
+    <row r="147" spans="1:9" ht="30" customHeight="1">
+      <c r="B147" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C147" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I147" s="12" t="s">
         <v>156</v>
-      </c>
-    </row>
-    <row r="147" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B147" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C147" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I147" s="12" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="148" spans="1:9" ht="13.5" customHeight="1">
@@ -2518,79 +2591,164 @@
         <v>35</v>
       </c>
       <c r="I148" s="12" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B149" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C149" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I149" s="12" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="149" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I149" s="12" t="s">
+    <row r="150" spans="1:9" ht="13.2" customHeight="1">
+      <c r="I150" s="12" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="150" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I150" s="12" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="151" spans="1:9" ht="28.8" customHeight="1">
+    <row r="151" spans="1:9" ht="31.2" customHeight="1">
       <c r="I151" s="12" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
     </row>
     <row r="152" spans="1:9" ht="28.8" customHeight="1">
       <c r="I152" s="12" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" ht="28.8" customHeight="1">
+      <c r="I153" s="12" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" ht="30.6" customHeight="1">
+      <c r="I154" s="12" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="153" spans="1:9" ht="30.6" customHeight="1">
-      <c r="I153" s="12" t="s">
+    <row r="155" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I155" s="12" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="154" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I154" s="12" t="s">
+    <row r="156" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A156" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="B156" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="C156" s="9"/>
+      <c r="I156" s="12"/>
+    </row>
+    <row r="157" spans="1:9" ht="30" customHeight="1">
+      <c r="A157" s="9"/>
+      <c r="I157" s="12" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="155" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A155" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B155" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="C155" s="9"/>
-      <c r="I155" s="12"/>
-    </row>
-    <row r="156" spans="1:9" ht="30" customHeight="1">
-      <c r="A156" s="9"/>
-      <c r="I156" s="12" t="s">
+    <row r="158" spans="1:9" ht="30.6" customHeight="1">
+      <c r="I158" s="12" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="157" spans="1:9" ht="30.6" customHeight="1">
-      <c r="I157" s="12" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="158" spans="1:9" ht="13.5" customHeight="1"/>
-    <row r="159" spans="1:9" ht="13.5" customHeight="1"/>
-    <row r="160" spans="1:9" ht="13.5" customHeight="1"/>
-    <row r="161" ht="13.5" customHeight="1"/>
-    <row r="162" ht="13.5" customHeight="1"/>
-    <row r="163" ht="13.5" customHeight="1"/>
-    <row r="164" ht="13.5" customHeight="1"/>
-    <row r="165" ht="13.5" customHeight="1"/>
-    <row r="166" ht="13.5" customHeight="1"/>
-    <row r="167" ht="13.5" customHeight="1"/>
-    <row r="168" ht="13.5" customHeight="1"/>
-    <row r="169" ht="13.5" customHeight="1"/>
-    <row r="170" ht="13.5" customHeight="1"/>
-    <row r="171" ht="13.5" customHeight="1"/>
-    <row r="172" ht="13.5" customHeight="1"/>
-    <row r="173" ht="13.5" customHeight="1"/>
-    <row r="174" ht="13.5" customHeight="1"/>
-    <row r="175" ht="13.5" customHeight="1"/>
-    <row r="176" ht="13.5" customHeight="1"/>
+    <row r="159" spans="1:9" ht="30" customHeight="1">
+      <c r="I159" s="12" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A160" s="9"/>
+      <c r="I160" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A161" s="9" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A162" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B163" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C163" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I163" s="12" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B164" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C164" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I164" s="12" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" ht="30" customHeight="1">
+      <c r="I165" s="12" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I166" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" ht="30" customHeight="1">
+      <c r="I167" s="12" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" ht="30" customHeight="1">
+      <c r="I168" s="12" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" ht="30.6" customHeight="1">
+      <c r="I169" s="12" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I170" s="12" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I171" s="12" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B172" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C172" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="174" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="175" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="176" spans="1:9" ht="13.5" customHeight="1"/>
     <row r="177" ht="13.5" customHeight="1"/>
     <row r="178" ht="13.5" customHeight="1"/>
     <row r="179" ht="13.5" customHeight="1"/>
@@ -2629,17 +2787,17 @@
     <row r="212" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="213" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="214" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="215" spans="1:2" ht="13.5" customHeight="1">
-      <c r="A215" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B215" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
+    <row r="215" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="216" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="217" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="218" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="218" spans="1:2" ht="13.5" customHeight="1">
+      <c r="A218" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
     <row r="219" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="220" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="221" spans="1:2" ht="13.5" customHeight="1"/>
@@ -3485,6 +3643,9 @@
     <row r="1061" ht="13.5" customHeight="1"/>
     <row r="1062" ht="13.5" customHeight="1"/>
     <row r="1063" ht="13.5" customHeight="1"/>
+    <row r="1064" ht="13.5" customHeight="1"/>
+    <row r="1065" ht="13.5" customHeight="1"/>
+    <row r="1066" ht="13.5" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Assets/test260903/chapter0106.xlsx
+++ b/Assets/test260903/chapter0106.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="467" documentId="11_AA3EC6FCFDC488042E83A027A8BF20349734F0B7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23FBF251-23DC-4C25-A702-336D6185B85A}"/>
+  <xr:revisionPtr revIDLastSave="525" documentId="11_AA3EC6FCFDC488042E83A027A8BF20349734F0B7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D0E95E9-CF40-4D4F-946C-554F78DA3DDE}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="187">
   <si>
     <t>Command</t>
   </si>
@@ -829,6 +829,18 @@
     <t>不意に甘く爽やかな香りがした。
 有希が一歩前に出たのだ</t>
     <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>喜び</t>
+  </si>
+  <si>
+    <t>怒り</t>
+  </si>
+  <si>
+    <t>悲しみ</t>
+  </si>
+  <si>
+    <t>照れ</t>
   </si>
 </sst>
 </file>
@@ -1368,7 +1380,7 @@
         <v>34</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>35</v>
+        <v>183</v>
       </c>
       <c r="I20" s="6" t="s">
         <v>33</v>
@@ -1407,8 +1419,8 @@
       <c r="B24" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C24" s="8" t="s">
-        <v>35</v>
+      <c r="C24" s="9" t="s">
+        <v>183</v>
       </c>
       <c r="I24" s="10" t="s">
         <v>41</v>
@@ -1419,7 +1431,7 @@
         <v>34</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>35</v>
+        <v>183</v>
       </c>
       <c r="I25" s="6" t="s">
         <v>42</v>
@@ -1447,7 +1459,7 @@
         <v>34</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>35</v>
+        <v>184</v>
       </c>
       <c r="I28" s="5" t="s">
         <v>45</v>
@@ -1516,7 +1528,7 @@
         <v>34</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>35</v>
+        <v>183</v>
       </c>
       <c r="I38" s="5" t="s">
         <v>53</v>
@@ -1577,7 +1589,7 @@
         <v>34</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>35</v>
+        <v>183</v>
       </c>
       <c r="I44" s="5" t="s">
         <v>59</v>
@@ -1706,7 +1718,7 @@
         <v>34</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>35</v>
+        <v>185</v>
       </c>
       <c r="I58" s="5" t="s">
         <v>73</v>
@@ -1801,7 +1813,7 @@
         <v>34</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>35</v>
+        <v>183</v>
       </c>
       <c r="I69" s="5" t="s">
         <v>84</v>
@@ -1845,7 +1857,7 @@
         <v>34</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>35</v>
+        <v>185</v>
       </c>
       <c r="I74" s="5" t="s">
         <v>89</v>
@@ -1875,8 +1887,8 @@
       <c r="B77" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C77" s="8" t="s">
-        <v>35</v>
+      <c r="C77" s="9" t="s">
+        <v>183</v>
       </c>
       <c r="I77" s="5" t="s">
         <v>92</v>
@@ -1887,7 +1899,7 @@
         <v>34</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>35</v>
+        <v>186</v>
       </c>
       <c r="I78" s="5" t="s">
         <v>93</v>
@@ -1918,7 +1930,7 @@
         <v>34</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>35</v>
+        <v>186</v>
       </c>
       <c r="I81" s="5" t="s">
         <v>96</v>
@@ -1981,7 +1993,7 @@
         <v>34</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>35</v>
+        <v>186</v>
       </c>
       <c r="I87" s="5" t="s">
         <v>101</v>
@@ -2066,7 +2078,7 @@
         <v>34</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>35</v>
+        <v>186</v>
       </c>
       <c r="I95" s="5" t="s">
         <v>111</v>
@@ -2077,7 +2089,7 @@
         <v>34</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>35</v>
+        <v>186</v>
       </c>
       <c r="I96" s="5" t="s">
         <v>112</v>
@@ -2087,8 +2099,8 @@
       <c r="B97" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C97" s="8" t="s">
-        <v>35</v>
+      <c r="C97" s="9" t="s">
+        <v>186</v>
       </c>
       <c r="I97" s="5" t="s">
         <v>113</v>
@@ -2115,8 +2127,8 @@
       <c r="B100" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C100" s="8" t="s">
-        <v>35</v>
+      <c r="C100" s="9" t="s">
+        <v>184</v>
       </c>
       <c r="I100" s="5" t="s">
         <v>115</v>
@@ -2127,7 +2139,7 @@
         <v>34</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>35</v>
+        <v>184</v>
       </c>
       <c r="I101" s="5" t="s">
         <v>116</v>
@@ -2138,7 +2150,7 @@
         <v>34</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>35</v>
+        <v>186</v>
       </c>
       <c r="I102" s="5" t="s">
         <v>117</v>
@@ -2207,8 +2219,8 @@
       <c r="B111" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C111" s="8" t="s">
-        <v>35</v>
+      <c r="C111" s="9" t="s">
+        <v>186</v>
       </c>
       <c r="I111" s="5" t="s">
         <v>124</v>
@@ -2218,8 +2230,8 @@
       <c r="B112" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C112" s="8" t="s">
-        <v>35</v>
+      <c r="C112" s="9" t="s">
+        <v>186</v>
       </c>
       <c r="I112" s="5" t="s">
         <v>125</v>
@@ -2230,7 +2242,7 @@
         <v>34</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>35</v>
+        <v>186</v>
       </c>
       <c r="I113" s="5" t="s">
         <v>126</v>
@@ -2308,7 +2320,7 @@
         <v>34</v>
       </c>
       <c r="C121" s="8" t="s">
-        <v>35</v>
+        <v>184</v>
       </c>
       <c r="I121" s="5" t="s">
         <v>132</v>
@@ -2357,7 +2369,7 @@
         <v>34</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>35</v>
+        <v>186</v>
       </c>
       <c r="I126" s="5" t="s">
         <v>137</v>
@@ -2460,7 +2472,7 @@
         <v>34</v>
       </c>
       <c r="C136" s="8" t="s">
-        <v>35</v>
+        <v>186</v>
       </c>
       <c r="H136" s="1"/>
       <c r="I136" s="5" t="s">
@@ -2473,7 +2485,7 @@
         <v>34</v>
       </c>
       <c r="C137" s="8" t="s">
-        <v>35</v>
+        <v>185</v>
       </c>
       <c r="H137" s="1"/>
       <c r="I137" s="5" t="s">
@@ -2554,8 +2566,8 @@
       <c r="B145" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C145" s="8" t="s">
-        <v>35</v>
+      <c r="C145" s="9" t="s">
+        <v>183</v>
       </c>
       <c r="I145" s="5" t="s">
         <v>154</v>
@@ -2566,7 +2578,7 @@
         <v>34</v>
       </c>
       <c r="C146" s="8" t="s">
-        <v>35</v>
+        <v>183</v>
       </c>
       <c r="I146" s="12" t="s">
         <v>155</v>
@@ -2577,7 +2589,7 @@
         <v>34</v>
       </c>
       <c r="C147" s="8" t="s">
-        <v>35</v>
+        <v>183</v>
       </c>
       <c r="I147" s="12" t="s">
         <v>156</v>
@@ -2587,8 +2599,8 @@
       <c r="B148" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C148" s="8" t="s">
-        <v>35</v>
+      <c r="C148" s="9" t="s">
+        <v>183</v>
       </c>
       <c r="I148" s="12" t="s">
         <v>157</v>
@@ -2598,8 +2610,8 @@
       <c r="B149" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C149" s="8" t="s">
-        <v>35</v>
+      <c r="C149" s="9" t="s">
+        <v>183</v>
       </c>
       <c r="I149" s="12" t="s">
         <v>158</v>
@@ -2685,7 +2697,7 @@
         <v>34</v>
       </c>
       <c r="C163" s="8" t="s">
-        <v>35</v>
+        <v>183</v>
       </c>
       <c r="I163" s="12" t="s">
         <v>170</v>
@@ -2695,8 +2707,8 @@
       <c r="B164" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C164" s="8" t="s">
-        <v>35</v>
+      <c r="C164" s="9" t="s">
+        <v>183</v>
       </c>
       <c r="I164" s="12" t="s">
         <v>171</v>
